--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488168_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488168_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3533</v>
+        <v>5.4069</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0147</v>
+        <v>4.2653</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3386</v>
+        <v>1.1416</v>
       </c>
       <c r="G2" t="n">
         <v>6.6556</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0788</v>
+        <v>0.1324</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1057</v>
+        <v>0.3563</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0269</v>
+        <v>-0.2239</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1959</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3603</v>
+        <v>3.8232</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8498</v>
+        <v>5.1895</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4895</v>
+        <v>-1.3663</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1003</v>
+        <v>-2.3845</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7833</v>
+        <v>2.9736</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4021</v>
+        <v>2.1896</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7647</v>
+        <v>-1.813</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3626</v>
+        <v>4.0026</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0851</v>
+        <v>-1.6005</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6644</v>
+        <v>-0.5715</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4207</v>
+        <v>-1.029</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0382</v>
+        <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1651</v>
+        <v>-0.3843</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0417</v>
+        <v>-0.1467</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1233</v>
+        <v>-0.2375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.9507</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2589</v>
+        <v>3.1466</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5659</v>
+        <v>-1.1959</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2869</v>
+        <v>2.8016</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1889</v>
+        <v>1.9498</v>
       </c>
       <c r="F4" t="n">
-        <v>1.098</v>
+        <v>0.8518</v>
       </c>
       <c r="G4" t="n">
         <v>2.228</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8841</v>
+        <v>0.3989</v>
       </c>
       <c r="T4" t="n">
-        <v>0.485</v>
+        <v>0.2459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3991</v>
+        <v>0.1529</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5664</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5117</v>
+        <v>1.8548</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2966</v>
+        <v>2.1965</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7849</v>
+        <v>-0.3418</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5891</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3845</v>
+        <v>1.1003</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9736</v>
+        <v>-1.7833</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1896</v>
+        <v>1.4021</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.813</v>
+        <v>1.7647</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0026</v>
+        <v>-0.3626</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6005</v>
+        <v>-2.0851</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5715</v>
+        <v>-0.6644</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.029</v>
+        <v>-1.4207</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6957</v>
+        <v>1.6595</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0396</v>
+        <v>1.3884</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6561</v>
+        <v>0.2711</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9507</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1466</v>
+        <v>1.2589</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1959</v>
+        <v>-0.5659</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.914</v>
+        <v>1.3183</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6392</v>
+        <v>0.8466</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2748</v>
+        <v>0.4718</v>
       </c>
       <c r="G6" t="n">
         <v>0.6747</v>
@@ -922,13 +922,13 @@
         <v>2.0382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2706</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2661</v>
+        <v>0.4735</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0045</v>
+        <v>0.2014</v>
       </c>
       <c r="V6" t="n">
         <v>1.6363</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1131</v>
+        <v>-0.1148</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6881</v>
+        <v>-0.3943</v>
       </c>
       <c r="F8" t="n">
-        <v>0.575</v>
+        <v>0.2796</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8141</v>
@@ -1078,13 +1078,13 @@
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8302</v>
+        <v>0.8285</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3246</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5056</v>
+        <v>0.2101</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3144</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9829</v>
+        <v>-0.2476</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9862</v>
+        <v>-0.3986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0033</v>
+        <v>0.1511</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8975</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3268</v>
+        <v>0.4085</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>0.4234</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1627</v>
+        <v>-0.0149</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0719</v>
+        <v>-1.9247</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.4196</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5543</v>
+        <v>-1.5051</v>
       </c>
       <c r="G10" t="n">
         <v>0.8217</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1525</v>
+        <v>-0.0053</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2589</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8337</v>
+        <v>-2.6625</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2404</v>
+        <v>-3.0445</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4066</v>
+        <v>0.382</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0877</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3198</v>
+        <v>-0.1486</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0584</v>
+        <v>0.1374</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2614</v>
+        <v>-0.286</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3144</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8977</v>
+        <v>-2.957</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3513</v>
+        <v>-1.1172</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2489</v>
+        <v>-1.8398</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9986</v>
+        <v>-3.3967</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5853</v>
+        <v>-1.5367</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4133</v>
+        <v>-1.8601</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3935</v>
+        <v>-1.2013</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0997</v>
+        <v>-1.2843</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7063</v>
+        <v>0.0829</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.6051</v>
+        <v>-2.1954</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4855</v>
+        <v>-0.2524</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1196</v>
+        <v>-1.943</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4895</v>
+        <v>-0.06</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4303</v>
+        <v>-0.2304</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0592</v>
+        <v>0.1704</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="W12" t="n">
         <v>0.3144</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9619</v>
+        <v>-3.186</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2699</v>
+        <v>0.1122</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.692</v>
+        <v>-3.2982</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3967</v>
+        <v>-3.9986</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5367</v>
+        <v>-2.5853</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8601</v>
+        <v>-1.4133</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2013</v>
+        <v>-0.3935</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2843</v>
+        <v>-1.0997</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0829</v>
+        <v>0.7063</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1954</v>
+        <v>-3.6051</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2524</v>
+        <v>-1.4855</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.943</v>
+        <v>-2.1196</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0649</v>
+        <v>0.2011</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.383</v>
+        <v>0.1912</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3181</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="W13" t="n">
         <v>0.3144</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.209099999999999</v>
+        <v>4.7563</v>
       </c>
       <c r="E14" t="n">
-        <v>9.282400000000001</v>
+        <v>9.829800000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-5.0733</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7356000000000007</v>
+        <v>0.7356000000000003</v>
       </c>
       <c r="H14" t="n">
         <v>-4.9472</v>
@@ -1522,10 +1522,10 @@
         <v>12.3773</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0141</v>
+        <v>0.01410000000000045</v>
       </c>
       <c r="L14" t="n">
-        <v>12.3635</v>
+        <v>12.36350000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-11.6418</v>
@@ -1537,7 +1537,7 @@
         <v>-6.6806</v>
       </c>
       <c r="P14" t="n">
-        <v>8.326672684688674e-17</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.9701</v>
@@ -1546,13 +1546,13 @@
         <v>12.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1586</v>
+        <v>3.7056</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9536</v>
+        <v>3.5006</v>
       </c>
       <c r="U14" t="n">
-        <v>0.205</v>
+        <v>0.2050000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.3150000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1807</v>
+        <v>6.3267</v>
       </c>
       <c r="E15" t="n">
-        <v>8.1646</v>
+        <v>8.458299999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9839</v>
+        <v>-2.1316</v>
       </c>
       <c r="G15" t="n">
         <v>4.6066</v>
@@ -1624,13 +1624,13 @@
         <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4989</v>
+        <v>-0.3529</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3109</v>
+        <v>-0.0171</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1881</v>
+        <v>-0.3358</v>
       </c>
       <c r="V15" t="n">
         <v>1.8877</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4571</v>
+        <v>2.5511</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2817</v>
+        <v>4.4004</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8247</v>
+        <v>-1.8493</v>
       </c>
       <c r="G16" t="n">
         <v>3.3756</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>0.767</v>
+        <v>-0.139</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0831</v>
+        <v>0.2018</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3161</v>
+        <v>-0.3407</v>
       </c>
       <c r="V16" t="n">
         <v>-0.315</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1187</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0714</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0473</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1381</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1903</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0522</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1961</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1724</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3686</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.058</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3627</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4207</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4808</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4873</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0065</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.8937</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9942</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.1005</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.1381</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.1903</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.0522</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.1961</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.1724</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3686</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.058</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.3627</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.4207</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.2559</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.4101</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.1542</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6093</v>
+        <v>0.7565</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5995</v>
+        <v>0.6974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0098</v>
+        <v>0.0591</v>
       </c>
       <c r="G19" t="n">
         <v>0.6312</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0219</v>
+        <v>0.1253</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6278</v>
+        <v>-0.3323</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1268</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.501</v>
+        <v>-0.2055</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1493</v>
@@ -2014,13 +2014,13 @@
         <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.2947</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0584</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5317</v>
+        <v>-0.2363</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9623</v>
+        <v>-0.6926</v>
       </c>
       <c r="E21" t="n">
-        <v>0.388</v>
+        <v>0.5838</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3503</v>
+        <v>-1.2764</v>
       </c>
       <c r="G21" t="n">
         <v>-0.31</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7466</v>
+        <v>-0.4769</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3656</v>
+        <v>-0.1697</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.381</v>
+        <v>-0.3072</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5733</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2566</v>
+        <v>-1.7915</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7652</v>
+        <v>-0.2756</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4914</v>
+        <v>-1.516</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6632</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1493</v>
+        <v>-0.6843</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6901</v>
+        <v>-0.2005</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4591</v>
+        <v>-0.4838</v>
       </c>
       <c r="V22" t="n">
         <v>0.6294</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5956</v>
+        <v>-5.1295</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1271</v>
+        <v>-2.8333</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4685</v>
+        <v>-2.2961</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2508</v>
@@ -2248,13 +2248,13 @@
         <v>2.2234</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2157</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3656</v>
+        <v>-0.0718</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8501</v>
+        <v>-0.6778</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5733</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.099</v>
+        <v>-7.7577</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.379099999999999</v>
+        <v>-7.7915</v>
       </c>
       <c r="F24" t="n">
-        <v>0.28</v>
+        <v>0.0338</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0803</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1839</v>
+        <v>-0.8425</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9302</v>
+        <v>-0.3426</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2537</v>
+        <v>-0.4999</v>
       </c>
       <c r="V24" t="n">
         <v>0.315</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.209300000000002</v>
+        <v>-4.2094</v>
       </c>
       <c r="E25" t="n">
-        <v>5.073200000000003</v>
+        <v>5.073099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.282700000000002</v>
+        <v>-9.282500000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7358999999999991</v>
@@ -2404,13 +2404,13 @@
         <v>12.9701</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.1587</v>
+        <v>-3.1586</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2050999999999999</v>
+        <v>-0.205</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.9535</v>
+        <v>-2.9536</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3150999999999999</v>
